--- a/files/港岛-筲箕湾-傲华.xlsx
+++ b/files/港岛-筲箕湾-傲华.xlsx
@@ -1114,7 +1114,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2025-01-27</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -1486,14 +1486,14 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
         <v>7762000</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>22630</v>
+        <v>22696</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>7762000</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>22630</v>
+        <v>22696</v>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2025-01-27</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -2416,7 +2416,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2602,7 +2602,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2025-01-27</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2025-01-27</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2025-01-27</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -3470,7 +3470,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -3594,7 +3594,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -3656,7 +3656,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -3718,7 +3718,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -3780,7 +3780,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -3842,7 +3842,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2025-01-07</t>
+          <t>2025-01-08</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2025-02-09</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -4028,7 +4028,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2025-04-06</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -4090,7 +4090,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -4152,7 +4152,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -4408,7 +4408,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2025-02-09</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -4470,7 +4470,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -4532,7 +4532,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -4718,7 +4718,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -4780,7 +4780,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -4842,7 +4842,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2025-02-09</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -5028,7 +5028,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -5090,7 +5090,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -5152,7 +5152,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -5214,7 +5214,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -5276,7 +5276,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2025-01-27</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -5400,7 +5400,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2025-01-27</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -5462,7 +5462,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2025-02-16</t>
+          <t>2025-02-17</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -5524,7 +5524,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -5586,7 +5586,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2025-02-09</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -5648,7 +5648,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2025-01-23</t>
+          <t>2025-01-24</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -5772,7 +5772,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -5834,7 +5834,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2025-02-04</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -5896,7 +5896,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2025-02-04</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -6020,7 +6020,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -6082,7 +6082,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -6144,7 +6144,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-11</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -6268,7 +6268,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2025-02-16</t>
+          <t>2025-02-17</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -6330,7 +6330,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2025-01-27</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -6392,7 +6392,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2025-02-04</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2025-02-04</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -6578,7 +6578,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2025-04-06</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -6640,7 +6640,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -6702,7 +6702,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -6764,7 +6764,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2025-01-27</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -6826,7 +6826,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2025-01-27</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
@@ -6888,7 +6888,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2025-01-27</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -6950,7 +6950,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2025-02-09</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2025-01-27</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
@@ -7074,7 +7074,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-21</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
@@ -7136,7 +7136,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2025-02-03</t>
+          <t>2025-02-04</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
@@ -7260,7 +7260,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2025-02-17</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -7322,7 +7322,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2025-01-27</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -7384,7 +7384,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2025-01-27</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -7446,7 +7446,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2025-01-23</t>
+          <t>2025-01-24</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
@@ -7508,7 +7508,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2025-02-02</t>
+          <t>2025-02-03</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -7570,7 +7570,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
@@ -7632,7 +7632,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="H113" s="5" t="n">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2025-02-04</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="H114" s="5" t="n">
@@ -7756,7 +7756,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2025-01-22</t>
+          <t>2025-01-23</t>
         </is>
       </c>
       <c r="H115" s="5" t="n">
@@ -7818,7 +7818,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2025-01-27</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="H116" s="5" t="n">
@@ -7880,7 +7880,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2025-01-23</t>
+          <t>2025-01-24</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
@@ -7942,7 +7942,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2025-02-11</t>
+          <t>2025-02-12</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -8004,7 +8004,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2025-01-27</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
@@ -8128,7 +8128,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="H121" s="5" t="n">
@@ -8190,7 +8190,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2025-01-27</t>
         </is>
       </c>
       <c r="H122" s="5" t="n">
@@ -8252,7 +8252,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2025-01-23</t>
+          <t>2025-01-24</t>
         </is>
       </c>
       <c r="H123" s="5" t="n">
@@ -8314,7 +8314,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2025-02-09</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="H124" s="5" t="n">
@@ -8376,7 +8376,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2025-01-27</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -8438,7 +8438,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2025-02-02</t>
+          <t>2025-02-03</t>
         </is>
       </c>
       <c r="H126" s="5" t="n">
@@ -8500,7 +8500,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2025-03-13</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="H127" s="5" t="n">
@@ -8562,7 +8562,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2025-01-27</t>
         </is>
       </c>
       <c r="H128" s="5" t="n">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="H129" s="5" t="n">
@@ -8686,7 +8686,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2025-01-27</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="H130" s="5" t="n">
@@ -8748,7 +8748,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2025-02-02</t>
+          <t>2025-02-03</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
@@ -8810,7 +8810,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2025-01-27</t>
         </is>
       </c>
       <c r="H132" s="5" t="n">
@@ -8872,7 +8872,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2025-01-27</t>
         </is>
       </c>
       <c r="H133" s="5" t="n">
@@ -8934,7 +8934,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2025-02-02</t>
+          <t>2025-02-03</t>
         </is>
       </c>
       <c r="H134" s="5" t="n">
@@ -8996,7 +8996,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2025-01-27</t>
         </is>
       </c>
       <c r="H135" s="5" t="n">
@@ -9058,7 +9058,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2025-02-11</t>
+          <t>2025-02-12</t>
         </is>
       </c>
       <c r="H136" s="5" t="n">
@@ -9120,7 +9120,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="H137" s="5" t="n">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2025-01-27</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="H138" s="5" t="n">
@@ -9244,7 +9244,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2025-02-05</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="H139" s="5" t="n">
@@ -9306,7 +9306,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2025-02-03</t>
+          <t>2025-02-04</t>
         </is>
       </c>
       <c r="H140" s="5" t="n">
@@ -9368,7 +9368,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2025-01-27</t>
         </is>
       </c>
       <c r="H141" s="5" t="n">
@@ -9430,7 +9430,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="H142" s="5" t="n">
@@ -9492,7 +9492,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>2025-02-17</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="H143" s="5" t="n">
@@ -9554,7 +9554,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2025-02-17</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="H144" s="5" t="n">
@@ -9616,7 +9616,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="H145" s="5" t="n">
@@ -9678,7 +9678,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2025-02-09</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="H146" s="5" t="n">
@@ -9740,7 +9740,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2025-02-12</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="H147" s="5" t="n">
@@ -9802,7 +9802,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2025-01-27</t>
         </is>
       </c>
       <c r="H148" s="5" t="n">
@@ -9864,7 +9864,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>2025-02-03</t>
+          <t>2025-02-04</t>
         </is>
       </c>
       <c r="H149" s="5" t="n">
@@ -9926,7 +9926,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>2025-02-03</t>
+          <t>2025-02-04</t>
         </is>
       </c>
       <c r="H150" s="5" t="n">
@@ -9988,7 +9988,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="H151" s="5" t="n">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="H152" s="5" t="n">
@@ -10112,7 +10112,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H153" s="5" t="n">
@@ -10174,7 +10174,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="H154" s="5" t="n">
@@ -10236,7 +10236,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="H155" s="5" t="n">
@@ -10298,7 +10298,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="H156" s="5" t="n">
@@ -10360,7 +10360,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="H157" s="5" t="n">
@@ -10422,7 +10422,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H158" s="5" t="n">
@@ -10651,10 +10651,10 @@
       </c>
       <c r="B6" s="22" t="inlineStr">
         <is>
-          <t>A | 343呎 (1房)
+          <t>A | 342呎 (1房)
 $776万
-$22,630/呎
-(26年-06月-19日)</t>
+$22,696/呎
+(26年-07月-28日)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -10662,7 +10662,7 @@
           <t>B | 211呎 (开放式)
 $444万
 $21,043/呎
-(25年-06月-01日)</t>
+(25年-06月-02日)</t>
         </is>
       </c>
       <c r="D6" s="22" t="inlineStr">
@@ -10670,7 +10670,7 @@
           <t>C | 220呎 (开放式)
 $420万
 $19,082/呎
-(25年-01月-26日)</t>
+(25年-01月-27日)</t>
         </is>
       </c>
       <c r="E6" s="23" t="inlineStr">
@@ -10694,7 +10694,7 @@
           <t>F | 456呎 (2房)
 $975万
 $21,382/呎
-(26年-02月-08日)</t>
+(26年-02月-09日)</t>
         </is>
       </c>
       <c r="H6" s="22" t="inlineStr">
@@ -10702,7 +10702,7 @@
           <t>G | 222呎 (开放式)
 $485万
 $21,856/呎
-(26年-01月-21日)</t>
+(26年-01月-22日)</t>
         </is>
       </c>
       <c r="I6" s="23" t="inlineStr">
@@ -10725,7 +10725,7 @@
           <t>A | 342呎 (1房)
 $756万
 $22,114/呎
-(26年-06月-10日)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -10733,7 +10733,7 @@
           <t>B | 211呎 (开放式)
 $434万
 $20,578/呎
-(25年-04月-08日)</t>
+(25年-04月-09日)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -10741,7 +10741,7 @@
           <t>C | 220呎 (开放式)
 $414万
 $18,823/呎
-(25年-02月-06日)</t>
+(25年-02月-07日)</t>
         </is>
       </c>
       <c r="E7" s="23" t="inlineStr">
@@ -10765,7 +10765,7 @@
           <t>F | 456呎 (2房)
 $969万
 $21,259/呎
-(26年-02月-26日)</t>
+(26年-02月-27日)</t>
         </is>
       </c>
       <c r="H7" s="22" t="inlineStr">
@@ -10773,7 +10773,7 @@
           <t>G | 222呎 (开放式)
 $498万
 $22,441/呎
-(26年-01月-15日)</t>
+(26年-01月-16日)</t>
         </is>
       </c>
       <c r="I7" s="23" t="inlineStr">
@@ -10796,7 +10796,7 @@
           <t>A | 342呎 (1房)
 $682万
 $19,942/呎
-(25年-12月-16日)</t>
+(25年-12月-17日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -10804,7 +10804,7 @@
           <t>B | 211呎 (开放式)
 $423万
 $20,062/呎
-(25年-03月-31日)</t>
+(25年-04月-01日)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -10812,7 +10812,7 @@
           <t>C | 220呎 (开放式)
 $404万
 $18,355/呎
-(25年-01月-26日)</t>
+(25年-01月-27日)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -10820,7 +10820,7 @@
           <t>D | 340呎 (1房)
 $784万
 $23,053/呎
-(26年-04月-16日)</t>
+(26年-04月-17日)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
@@ -10828,7 +10828,7 @@
           <t>E | 324呎 (1房)
 $688万
 $21,241/呎
-(25年-10月-08日)</t>
+(25年-10月-09日)</t>
         </is>
       </c>
       <c r="G8" s="22" t="inlineStr">
@@ -10836,7 +10836,7 @@
           <t>F | 456呎 (2房)
 $946万
 $20,741/呎
-(26年-03月-02日)</t>
+(26年-03月-03日)</t>
         </is>
       </c>
       <c r="H8" s="22" t="inlineStr">
@@ -10844,7 +10844,7 @@
           <t>G | 222呎 (开放式)
 $454万
 $20,468/呎
-(25年-11月-20日)</t>
+(25年-11月-21日)</t>
         </is>
       </c>
       <c r="I8" s="23" t="inlineStr">
@@ -10867,7 +10867,7 @@
           <t>A | 342呎 (1房)
 $665万
 $19,450/呎
-(25年-11月-13日)</t>
+(25年-11月-14日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -10875,7 +10875,7 @@
           <t>B | 211呎 (开放式)
 $422万
 $20,000/呎
-(25年-01月-26日)</t>
+(25年-01月-27日)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -10883,7 +10883,7 @@
           <t>C | 220呎 (开放式)
 $398万
 $18,109/呎
-(25年-01月-26日)</t>
+(25年-01月-27日)</t>
         </is>
       </c>
       <c r="E9" s="23" t="inlineStr">
@@ -10899,7 +10899,7 @@
           <t>E | 324呎 (1房)
 $679万
 $20,948/呎
-(25年-10月-15日)</t>
+(25年-10月-16日)</t>
         </is>
       </c>
       <c r="G9" s="22" t="inlineStr">
@@ -10907,7 +10907,7 @@
           <t>F | 456呎 (2房)
 $934万
 $20,474/呎
-(26年-02月-09日)</t>
+(26年-02月-10日)</t>
         </is>
       </c>
       <c r="H9" s="22" t="inlineStr">
@@ -10915,7 +10915,7 @@
           <t>G | 222呎 (开放式)
 $444万
 $20,018/呎
-(25年-12月-11日)</t>
+(25年-12月-12日)</t>
         </is>
       </c>
       <c r="I9" s="22" t="inlineStr">
@@ -10923,7 +10923,7 @@
           <t>H | 283呎 (1房)
 $598万
 $21,117/呎
-(25年-12月-07日)</t>
+(25年-12月-08日)</t>
         </is>
       </c>
     </row>
@@ -10938,7 +10938,7 @@
           <t>A | 343呎 (1房)
 $656万
 $19,125/呎
-(25年-05月-14日)</t>
+(25年-05月-15日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -10946,7 +10946,7 @@
           <t>B | 211呎 (开放式)
 $416万
 $19,697/呎
-(25年-02月-18日)</t>
+(25年-02月-19日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -10954,7 +10954,7 @@
           <t>C | 220呎 (开放式)
 $393万
 $17,859/呎
-(25年-01月-26日)</t>
+(25年-01月-27日)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -10962,7 +10962,7 @@
           <t>D | 340呎 (1房)
 $698万
 $20,541/呎
-(25年-10月-23日)</t>
+(25年-10月-24日)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -10970,7 +10970,7 @@
           <t>E | 324呎 (1房)
 $691万
 $21,336/呎
-(25年-11月-06日)</t>
+(25年-11月-07日)</t>
         </is>
       </c>
       <c r="G10" s="22" t="inlineStr">
@@ -10978,7 +10978,7 @@
           <t>F | 456呎 (2房)
 $920万
 $20,175/呎
-(26年-02月-02日)</t>
+(26年-02月-03日)</t>
         </is>
       </c>
       <c r="H10" s="22" t="inlineStr">
@@ -10986,7 +10986,7 @@
           <t>G | 222呎 (开放式)
 $438万
 $19,743/呎
-(25年-12月-03日)</t>
+(25年-12月-04日)</t>
         </is>
       </c>
       <c r="I10" s="22" t="inlineStr">
@@ -10994,7 +10994,7 @@
           <t>H | 283呎 (1房)
 $589万
 $20,827/呎
-(25年-11月-17日)</t>
+(25年-11月-18日)</t>
         </is>
       </c>
     </row>
@@ -11009,7 +11009,7 @@
           <t>A | 342呎 (1房)
 $654万
 $19,123/呎
-(25年-12月-04日)</t>
+(25年-12月-05日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -11017,7 +11017,7 @@
           <t>B | 211呎 (开放式)
 $410万
 $19,427/呎
-(25年-02月-09日)</t>
+(25年-02月-10日)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -11025,7 +11025,7 @@
           <t>C | 220呎 (开放式)
 $388万
 $17,618/呎
-(25年-01月-07日)</t>
+(25年-01月-08日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -11033,7 +11033,7 @@
           <t>D | 340呎 (1房)
 $689万
 $20,259/呎
-(25年-11月-12日)</t>
+(25年-11月-13日)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -11041,7 +11041,7 @@
           <t>E | 324呎 (1房)
 $660万
 $20,367/呎
-(25年-10月-23日)</t>
+(25年-10月-24日)</t>
         </is>
       </c>
       <c r="G11" s="22" t="inlineStr">
@@ -11049,7 +11049,7 @@
           <t>F | 456呎 (2房)
 $966万
 $21,189/呎
-(25年-10月-23日)</t>
+(25年-10月-24日)</t>
         </is>
       </c>
       <c r="H11" s="22" t="inlineStr">
@@ -11057,7 +11057,7 @@
           <t>G | 222呎 (开放式)
 $441万
 $19,865/呎
-(25年-11月-27日)</t>
+(25年-11月-28日)</t>
         </is>
       </c>
       <c r="I11" s="22" t="inlineStr">
@@ -11065,7 +11065,7 @@
           <t>H | 283呎 (1房)
 $581万
 $20,537/呎
-(25年-11月-11日)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
     </row>
@@ -11080,7 +11080,7 @@
           <t>A | 342呎 (1房)
 $638万
 $18,655/呎
-(25年-12月-10日)</t>
+(25年-12月-11日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -11088,7 +11088,7 @@
           <t>B | 211呎 (开放式)
 $404万
 $19,161/呎
-(25年-02月-09日)</t>
+(25年-02月-10日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -11096,7 +11096,7 @@
           <t>C | 220呎 (开放式)
 $402万
 $18,250/呎
-(25年-02月-24日)</t>
+(25年-02月-25日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -11104,7 +11104,7 @@
           <t>D | 340呎 (1房)
 $679万
 $19,976/呎
-(25年-10月-30日)</t>
+(25年-10月-31日)</t>
         </is>
       </c>
       <c r="F12" s="20" t="inlineStr">
@@ -11120,7 +11120,7 @@
           <t>F | 456呎 (2房)
 $954万
 $20,914/呎
-(25年-10月-13日)</t>
+(25年-10月-14日)</t>
         </is>
       </c>
       <c r="H12" s="22" t="inlineStr">
@@ -11128,7 +11128,7 @@
           <t>G | 221呎 (开放式)
 $426万
 $19,299/呎
-(25年-08月-14日)</t>
+(25年-08月-15日)</t>
         </is>
       </c>
       <c r="I12" s="22" t="inlineStr">
@@ -11136,7 +11136,7 @@
           <t>H | 283呎 (1房)
 $573万
 $20,254/呎
-(25年-04月-06日)</t>
+(25年-04月-07日)</t>
         </is>
       </c>
     </row>
@@ -11151,7 +11151,7 @@
           <t>A | 342呎 (1房)
 $629万
 $18,401/呎
-(25年-08月-28日)</t>
+(25年-08月-29日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -11159,7 +11159,7 @@
           <t>B | 211呎 (开放式)
 $399万
 $18,900/呎
-(25年-02月-09日)</t>
+(25年-02月-10日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -11167,7 +11167,7 @@
           <t>C | 220呎 (开放式)
 $377万
 $17,145/呎
-(25年-02月-06日)</t>
+(25年-02月-07日)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -11175,7 +11175,7 @@
           <t>D | 340呎 (1房)
 $670万
 $19,703/呎
-(25年-10月-29日)</t>
+(25年-10月-30日)</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -11183,7 +11183,7 @@
           <t>E | 324呎 (1房)
 $642万
 $19,812/呎
-(25年-09月-25日)</t>
+(25年-09月-26日)</t>
         </is>
       </c>
       <c r="G13" s="22" t="inlineStr">
@@ -11191,7 +11191,7 @@
           <t>F | 456呎 (2房)
 $941万
 $20,645/呎
-(25年-10月-15日)</t>
+(25年-10月-16日)</t>
         </is>
       </c>
       <c r="H13" s="22" t="inlineStr">
@@ -11199,7 +11199,7 @@
           <t>G | 221呎 (开放式)
 $425万
 $19,213/呎
-(25年-07月-14日)</t>
+(25年-07月-15日)</t>
         </is>
       </c>
       <c r="I13" s="22" t="inlineStr">
@@ -11207,7 +11207,7 @@
           <t>H | 283呎 (1房)
 $565万
 $19,972/呎
-(25年-10月-29日)</t>
+(25年-10月-30日)</t>
         </is>
       </c>
     </row>
@@ -11222,7 +11222,7 @@
           <t>A | 343呎 (1房)
 $620万
 $18,090/呎
-(25年-02月-16日)</t>
+(25年-02月-17日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -11230,7 +11230,7 @@
           <t>B | 211呎 (开放式)
 $394万
 $18,649/呎
-(25年-01月-26日)</t>
+(25年-01月-27日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -11238,7 +11238,7 @@
           <t>C | 220呎 (开放式)
 $372万
 $16,918/呎
-(25年-01月-27日)</t>
+(25年-01月-28日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -11246,7 +11246,7 @@
           <t>D | 340呎 (1房)
 $661万
 $19,432/呎
-(25年-08月-25日)</t>
+(25年-08月-26日)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -11254,7 +11254,7 @@
           <t>E | 324呎 (1房)
 $633万
 $19,540/呎
-(25年-07月-01日)</t>
+(25年-07月-02日)</t>
         </is>
       </c>
       <c r="G14" s="22" t="inlineStr">
@@ -11262,7 +11262,7 @@
           <t>F | 456呎 (2房)
 $929万
 $20,382/呎
-(25年-08月-14日)</t>
+(25年-08月-15日)</t>
         </is>
       </c>
       <c r="H14" s="22" t="inlineStr">
@@ -11270,7 +11270,7 @@
           <t>G | 221呎 (开放式)
 $415万
 $18,783/呎
-(25年-06月-16日)</t>
+(25年-06月-17日)</t>
         </is>
       </c>
       <c r="I14" s="22" t="inlineStr">
@@ -11278,7 +11278,7 @@
           <t>H | 283呎 (1房)
 $557万
 $19,696/呎
-(25年-06月-07日)</t>
+(25年-06月-08日)</t>
         </is>
       </c>
     </row>
@@ -11293,7 +11293,7 @@
           <t>A | 343呎 (1房)
 $612万
 $17,843/呎
-(25年-02月-04日)</t>
+(25年-02月-05日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -11301,7 +11301,7 @@
           <t>B | 211呎 (开放式)
 $388万
 $18,393/呎
-(25年-02月-06日)</t>
+(25年-02月-07日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -11309,7 +11309,7 @@
           <t>C | 220呎 (开放式)
 $367万
 $16,686/呎
-(25年-02月-04日)</t>
+(25年-02月-05日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -11317,7 +11317,7 @@
           <t>D | 340呎 (1房)
 $652万
 $19,162/呎
-(25年-04月-10日)</t>
+(25年-04月-11日)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -11325,7 +11325,7 @@
           <t>E | 324呎 (1房)
 $624万
 $19,272/呎
-(25年-01月-23日)</t>
+(25年-01月-24日)</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -11333,7 +11333,7 @@
           <t>F | 456呎 (2房)
 $918万
 $20,121/呎
-(25年-07月-09日)</t>
+(25年-07月-10日)</t>
         </is>
       </c>
       <c r="H15" s="22" t="inlineStr">
@@ -11341,7 +11341,7 @@
           <t>G | 221呎 (开放式)
 $413万
 $18,692/呎
-(25年-02月-09日)</t>
+(25年-02月-10日)</t>
         </is>
       </c>
       <c r="I15" s="22" t="inlineStr">
@@ -11349,7 +11349,7 @@
           <t>H | 283呎 (1房)
 $550万
 $19,431/呎
-(25年-05月-13日)</t>
+(25年-05月-14日)</t>
         </is>
       </c>
     </row>
@@ -11364,7 +11364,7 @@
           <t>A | 343呎 (1房)
 $604万
 $17,595/呎
-(25年-02月-04日)</t>
+(25年-02月-05日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -11372,7 +11372,7 @@
           <t>B | 211呎 (开放式)
 $383万
 $18,137/呎
-(25年-02月-04日)</t>
+(25年-02月-05日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -11380,7 +11380,7 @@
           <t>C | 220呎 (开放式)
 $362万
 $16,464/呎
-(25年-01月-27日)</t>
+(25年-01月-28日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -11388,7 +11388,7 @@
           <t>D | 340呎 (1房)
 $643万
 $18,900/呎
-(25年-02月-16日)</t>
+(25年-02月-17日)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -11396,7 +11396,7 @@
           <t>E | 324呎 (1房)
 $616万
 $19,000/呎
-(25年-02月-10日)</t>
+(25年-02月-11日)</t>
         </is>
       </c>
       <c r="G16" s="22" t="inlineStr">
@@ -11404,7 +11404,7 @@
           <t>F | 456呎 (2房)
 $922万
 $20,226/呎
-(25年-11月-03日)</t>
+(25年-11月-04日)</t>
         </is>
       </c>
       <c r="H16" s="22" t="inlineStr">
@@ -11412,7 +11412,7 @@
           <t>G | 221呎 (开放式)
 $408万
 $18,443/呎
-(25年-05月-19日)</t>
+(25年-05月-20日)</t>
         </is>
       </c>
       <c r="I16" s="22" t="inlineStr">
@@ -11420,7 +11420,7 @@
           <t>H | 283呎 (1房)
 $542万
 $19,159/呎
-(25年-06月-26日)</t>
+(25年-06月-27日)</t>
         </is>
       </c>
     </row>
@@ -11435,7 +11435,7 @@
           <t>A | 343呎 (1房)
 $595万
 $17,353/呎
-(25年-02月-09日)</t>
+(25年-02月-10日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -11443,7 +11443,7 @@
           <t>B | 211呎 (开放式)
 $374万
 $17,720/呎
-(25年-01月-27日)</t>
+(25年-01月-28日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -11451,7 +11451,7 @@
           <t>C | 220呎 (开放式)
 $353万
 $16,064/呎
-(25年-01月-26日)</t>
+(25年-01月-27日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -11459,7 +11459,7 @@
           <t>D | 340呎 (1房)
 $634万
 $18,632/呎
-(25年-01月-26日)</t>
+(25年-01月-27日)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -11467,7 +11467,7 @@
           <t>E | 324呎 (1房)
 $607万
 $18,741/呎
-(25年-02月-06日)</t>
+(25年-02月-07日)</t>
         </is>
       </c>
       <c r="G17" s="22" t="inlineStr">
@@ -11475,7 +11475,7 @@
           <t>F | 456呎 (2房)
 $894万
 $19,607/呎
-(25年-06月-01日)</t>
+(25年-06月-02日)</t>
         </is>
       </c>
       <c r="H17" s="22" t="inlineStr">
@@ -11483,7 +11483,7 @@
           <t>G | 221呎 (开放式)
 $398万
 $18,023/呎
-(25年-04月-06日)</t>
+(25年-04月-07日)</t>
         </is>
       </c>
       <c r="I17" s="22" t="inlineStr">
@@ -11491,7 +11491,7 @@
           <t>H | 283呎 (1房)
 $535万
 $18,894/呎
-(25年-03月-31日)</t>
+(25年-04月-01日)</t>
         </is>
       </c>
     </row>
@@ -11506,7 +11506,7 @@
           <t>A | 343呎 (1房)
 $587万
 $17,114/呎
-(25年-01月-23日)</t>
+(25年-01月-24日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -11514,7 +11514,7 @@
           <t>B | 211呎 (开放式)
 $372万
 $17,654/呎
-(25年-01月-26日)</t>
+(25年-01月-27日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -11522,7 +11522,7 @@
           <t>C | 220呎 (开放式)
 $352万
 $16,018/呎
-(25年-01月-26日)</t>
+(25年-01月-27日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -11530,7 +11530,7 @@
           <t>D | 340呎 (1房)
 $652万
 $19,185/呎
-(25年-02月-17日)</t>
+(25年-02月-18日)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -11538,7 +11538,7 @@
           <t>E | 324呎 (1房)
 $599万
 $18,485/呎
-(25年-02月-03日)</t>
+(25年-02月-04日)</t>
         </is>
       </c>
       <c r="G18" s="22" t="inlineStr">
@@ -11546,7 +11546,7 @@
           <t>F | 456呎 (2房)
 $883万
 $19,355/呎
-(25年-05月-01日)</t>
+(25年-05月-02日)</t>
         </is>
       </c>
       <c r="H18" s="22" t="inlineStr">
@@ -11554,7 +11554,7 @@
           <t>G | 221呎 (开放式)
 $397万
 $17,950/呎
-(25年-02月-20日)</t>
+(25年-02月-21日)</t>
         </is>
       </c>
       <c r="I18" s="22" t="inlineStr">
@@ -11562,7 +11562,7 @@
           <t>H | 283呎 (1房)
 $527万
 $18,633/呎
-(25年-01月-27日)</t>
+(25年-01月-28日)</t>
         </is>
       </c>
     </row>
@@ -11577,7 +11577,7 @@
           <t>A | 343呎 (1房)
 $580万
 $16,895/呎
-(25年-02月-11日)</t>
+(25年-02月-12日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -11585,7 +11585,7 @@
           <t>B | 211呎 (开放式)
 $368万
 $17,431/呎
-(25年-01月-23日)</t>
+(25年-01月-24日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -11593,7 +11593,7 @@
           <t>C | 220呎 (开放式)
 $348万
 $15,818/呎
-(25年-01月-27日)</t>
+(25年-01月-28日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -11601,7 +11601,7 @@
           <t>D | 340呎 (1房)
 $617万
 $18,144/呎
-(25年-01月-22日)</t>
+(25年-01月-23日)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -11609,7 +11609,7 @@
           <t>E | 324呎 (1房)
 $617万
 $19,046/呎
-(25年-02月-04日)</t>
+(25年-02月-05日)</t>
         </is>
       </c>
       <c r="G19" s="22" t="inlineStr">
@@ -11617,7 +11617,7 @@
           <t>F | 456呎 (2房)
 $871万
 $19,105/呎
-(25年-08月-21日)</t>
+(25年-08月-22日)</t>
         </is>
       </c>
       <c r="H19" s="22" t="inlineStr">
@@ -11625,7 +11625,7 @@
           <t>G | 221呎 (开放式)
 $392万
 $17,724/呎
-(25年-02月-26日)</t>
+(25年-02月-27日)</t>
         </is>
       </c>
       <c r="I19" s="22" t="inlineStr">
@@ -11633,7 +11633,7 @@
           <t>H | 283呎 (1房)
 $521万
 $18,396/呎
-(25年-02月-02日)</t>
+(25年-02月-03日)</t>
         </is>
       </c>
     </row>
@@ -11648,7 +11648,7 @@
           <t>A | 342呎 (1房)
 $597万
 $17,462/呎
-(25年-02月-02日)</t>
+(25年-02月-03日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -11656,7 +11656,7 @@
           <t>B | 211呎 (开放式)
 $359万
 $17,033/呎
-(25年-01月-26日)</t>
+(25年-01月-27日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -11664,7 +11664,7 @@
           <t>C | 220呎 (开放式)
 $340万
 $15,445/呎
-(25年-02月-09日)</t>
+(25年-02月-10日)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -11672,7 +11672,7 @@
           <t>D | 340呎 (1房)
 $609万
 $17,912/呎
-(25年-01月-23日)</t>
+(25年-01月-24日)</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -11680,7 +11680,7 @@
           <t>E | 324呎 (1房)
 $584万
 $18,012/呎
-(25年-01月-26日)</t>
+(25年-01月-27日)</t>
         </is>
       </c>
       <c r="G20" s="22" t="inlineStr">
@@ -11688,7 +11688,7 @@
           <t>F | 456呎 (2房)
 $860万
 $18,862/呎
-(25年-08月-05日)</t>
+(25年-08月-06日)</t>
         </is>
       </c>
       <c r="H20" s="22" t="inlineStr">
@@ -11696,7 +11696,7 @@
           <t>G | 221呎 (开放式)
 $387万
 $17,507/呎
-(25年-01月-26日)</t>
+(25年-01月-27日)</t>
         </is>
       </c>
       <c r="I20" s="22" t="inlineStr">
@@ -11704,7 +11704,7 @@
           <t>H | 283呎 (1房)
 $514万
 $18,163/呎
-(25年-03月-18日)</t>
+(25年-03月-19日)</t>
         </is>
       </c>
     </row>
@@ -11719,7 +11719,7 @@
           <t>A | 342呎 (1房)
 $565万
 $16,512/呎
-(25年-02月-02日)</t>
+(25年-02月-03日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -11727,7 +11727,7 @@
           <t>B | 211呎 (开放式)
 $349万
 $16,559/呎
-(25年-01月-26日)</t>
+(25年-01月-27日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -11735,7 +11735,7 @@
           <t>C | 220呎 (开放式)
 $339万
 $15,418/呎
-(25年-01月-26日)</t>
+(25年-01月-27日)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -11743,7 +11743,7 @@
           <t>D | 340呎 (1房)
 $601万
 $17,679/呎
-(25年-02月-02日)</t>
+(25年-02月-03日)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -11751,7 +11751,7 @@
           <t>E | 324呎 (1房)
 $576万
 $17,778/呎
-(25年-01月-27日)</t>
+(25年-01月-28日)</t>
         </is>
       </c>
       <c r="G21" s="22" t="inlineStr">
@@ -11759,7 +11759,7 @@
           <t>F | 456呎 (2房)
 $849万
 $18,618/呎
-(25年-07月-22日)</t>
+(25年-07月-23日)</t>
         </is>
       </c>
       <c r="H21" s="22" t="inlineStr">
@@ -11767,7 +11767,7 @@
           <t>G | 221呎 (开放式)
 $382万
 $17,285/呎
-(25年-01月-26日)</t>
+(25年-01月-27日)</t>
         </is>
       </c>
       <c r="I21" s="22" t="inlineStr">
@@ -11775,7 +11775,7 @@
           <t>H | 283呎 (1房)
 $507万
 $17,926/呎
-(25年-03月-13日)</t>
+(25年-03月-14日)</t>
         </is>
       </c>
     </row>
@@ -11790,7 +11790,7 @@
           <t>A | 343呎 (1房)
 $548万
 $15,968/呎
-(25年-03月-24日)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -11798,7 +11798,7 @@
           <t>B | 211呎 (开放式)
 $341万
 $16,175/呎
-(25年-01月-26日)</t>
+(25年-01月-27日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -11806,7 +11806,7 @@
           <t>C | 220呎 (开放式)
 $335万
 $15,232/呎
-(25年-02月-03日)</t>
+(25年-02月-04日)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -11814,7 +11814,7 @@
           <t>D | 340呎 (1房)
 $601万
 $17,682/呎
-(25年-02月-05日)</t>
+(25年-02月-06日)</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -11822,7 +11822,7 @@
           <t>E | 324呎 (1房)
 $595万
 $18,358/呎
-(25年-01月-27日)</t>
+(25年-01月-28日)</t>
         </is>
       </c>
       <c r="G22" s="22" t="inlineStr">
@@ -11830,7 +11830,7 @@
           <t>F | 456呎 (2房)
 $838万
 $18,382/呎
-(25年-05月-13日)</t>
+(25年-05月-14日)</t>
         </is>
       </c>
       <c r="H22" s="22" t="inlineStr">
@@ -11838,7 +11838,7 @@
           <t>G | 221呎 (开放式)
 $377万
 $17,068/呎
-(25年-02月-11日)</t>
+(25年-02月-12日)</t>
         </is>
       </c>
       <c r="I22" s="22" t="inlineStr">
@@ -11846,7 +11846,7 @@
           <t>H | 283呎 (1房)
 $517万
 $18,279/呎
-(25年-01月-26日)</t>
+(25年-01月-27日)</t>
         </is>
       </c>
     </row>
@@ -11861,7 +11861,7 @@
           <t>A | 343呎 (1房)
 $548万
 $15,968/呎
-(25年-02月-03日)</t>
+(25年-02月-04日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -11869,7 +11869,7 @@
           <t>B | 211呎 (开放式)
 $345万
 $16,355/呎
-(25年-02月-03日)</t>
+(25年-02月-04日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -11877,7 +11877,7 @@
           <t>C | 220呎 (开放式)
 $335万
 $15,232/呎
-(25年-01月-26日)</t>
+(25年-01月-27日)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -11885,7 +11885,7 @@
           <t>D | 340呎 (1房)
 $595万
 $17,491/呎
-(25年-02月-12日)</t>
+(25年-02月-13日)</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -11893,7 +11893,7 @@
           <t>E | 324呎 (1房)
 $570万
 $17,586/呎
-(25年-02月-09日)</t>
+(25年-02月-10日)</t>
         </is>
       </c>
       <c r="G23" s="22" t="inlineStr">
@@ -11901,7 +11901,7 @@
           <t>F | 456呎 (2房)
 $838万
 $18,382/呎
-(25年-06月-17日)</t>
+(25年-06月-18日)</t>
         </is>
       </c>
       <c r="H23" s="22" t="inlineStr">
@@ -11909,7 +11909,7 @@
           <t>G | 222呎 (开放式)
 $377万
 $16,991/呎
-(25年-02月-17日)</t>
+(25年-02月-18日)</t>
         </is>
       </c>
       <c r="I23" s="22" t="inlineStr">
@@ -11917,7 +11917,7 @@
           <t>H | 283呎 (1房)
 $501万
 $17,696/呎
-(25年-02月-17日)</t>
+(25年-02月-18日)</t>
         </is>
       </c>
     </row>
@@ -11932,7 +11932,7 @@
           <t>A | 305呎 (1房)
 $738万
 $24,203/呎
-(26年-04月-16日)</t>
+(26年-04月-17日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -11940,7 +11940,7 @@
           <t>B | 190呎 (开放式)
 $393万
 $20,674/呎
-(25年-05月-12日)</t>
+(25年-05月-13日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -11948,7 +11948,7 @@
           <t>C | 197呎 (开放式)
 $378万
 $19,173/呎
-(25年-05月-13日)</t>
+(25年-05月-14日)</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -11956,7 +11956,7 @@
           <t>D | 300呎 (1房)
 $679万
 $22,620/呎
-(25年-11月-27日)</t>
+(25年-11月-28日)</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -11964,7 +11964,7 @@
           <t>E | 285呎 (1房)
 $646万
 $22,667/呎
-(25年-08月-21日)</t>
+(25年-08月-22日)</t>
         </is>
       </c>
       <c r="G24" s="22" t="inlineStr">
@@ -11972,7 +11972,7 @@
           <t>F | 417呎 (2房)
 $1115万
 $26,739/呎
-(26年-05月-28日)</t>
+(26年-05月-29日)</t>
         </is>
       </c>
       <c r="H24" s="22" t="inlineStr">
@@ -11980,7 +11980,7 @@
           <t>G | 198呎 (开放式)
 $416万
 $20,985/呎
-(25年-05月-26日)</t>
+(25年-05月-27日)</t>
         </is>
       </c>
       <c r="I24" s="22" t="inlineStr">
@@ -11988,7 +11988,7 @@
           <t>H | 246呎 (1房)
 $556万
 $22,585/呎
-(25年-05月-01日)</t>
+(25年-05月-02日)</t>
         </is>
       </c>
     </row>

--- a/files/港岛-筲箕湾-傲华.xlsx
+++ b/files/港岛-筲箕湾-傲华.xlsx
@@ -1791,34 +1791,34 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
-        <v>8474000</v>
+        <v>8050000</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>24924</v>
+        <v>23676</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K19" s="5" t="n">
-        <v>8050300</v>
+        <v>8050000</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>23677</v>
+        <v>23676</v>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>120天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
@@ -3284,14 +3284,14 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
-        <v>6984000</v>
+        <v>7622000</v>
       </c>
       <c r="I43" s="5" t="n">
-        <v>20541</v>
+        <v>22418</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
@@ -3299,10 +3299,10 @@
         </is>
       </c>
       <c r="K43" s="5" t="n">
-        <v>6984000</v>
+        <v>7622000</v>
       </c>
       <c r="L43" s="5" t="n">
-        <v>20541</v>
+        <v>22418</v>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
@@ -10529,7 +10529,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -10539,7 +10539,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>144</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -10744,12 +10744,12 @@
 (25年-02月-07日)</t>
         </is>
       </c>
-      <c r="E7" s="23" t="inlineStr">
+      <c r="E7" s="22" t="inlineStr">
         <is>
           <t>D | 340呎 (1房)
-$847万
-$24,924/呎
-(在售)</t>
+$805万
+$23,676/呎
+(26年-08月-14日)</t>
         </is>
       </c>
       <c r="F7" s="23" t="inlineStr">
@@ -10960,9 +10960,9 @@
       <c r="E10" s="22" t="inlineStr">
         <is>
           <t>D | 340呎 (1房)
-$698万
-$20,541/呎
-(25年-10月-24日)</t>
+$762万
+$22,418/呎
+(26年-08月-14日)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">

--- a/files/港岛-筲箕湾-傲华.xlsx
+++ b/files/港岛-筲箕湾-傲华.xlsx
@@ -2783,34 +2783,34 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
-        <v>8135000</v>
+        <v>7728000</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>23926</v>
+        <v>22729</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K35" s="5" t="n">
-        <v>7728250</v>
+        <v>7728000</v>
       </c>
       <c r="L35" s="5" t="n">
-        <v>22730</v>
+        <v>22729</v>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>180天醫護專業付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
@@ -4209,38 +4209,30 @@
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H58" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I58" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="H58" s="5" t="n">
+        <v>7776000</v>
+      </c>
+      <c r="I58" s="5" t="n">
+        <v>24000</v>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K58" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L58" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+      <c r="K58" s="5" t="n">
+        <v>7776000</v>
+      </c>
+      <c r="L58" s="5" t="n">
+        <v>24000</v>
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
@@ -10529,7 +10521,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -10539,7 +10531,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>146</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -10549,7 +10541,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -10886,12 +10878,12 @@
 (25年-01月-27日)</t>
         </is>
       </c>
-      <c r="E9" s="23" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t>D | 340呎 (1房)
-$814万
-$23,926/呎
-(在售)</t>
+$773万
+$22,729/呎
+(26年-08月-22日)</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
@@ -11107,12 +11099,12 @@
 (25年-10月-31日)</t>
         </is>
       </c>
-      <c r="F12" s="20" t="inlineStr">
+      <c r="F12" s="22" t="inlineStr">
         <is>
           <t>E | 324呎 (1房)
--
--
-(待售)</t>
+$778万
+$24,000/呎
+(26年-08月-22日)</t>
         </is>
       </c>
       <c r="G12" s="22" t="inlineStr">

--- a/files/港岛-筲箕湾-傲华.xlsx
+++ b/files/港岛-筲箕湾-傲华.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -116,18 +116,13 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
       <sz val="8"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
       <color rgb="00660000"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
       <sz val="8"/>
     </font>
   </fonts>
@@ -207,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -266,16 +261,13 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -767,7 +759,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -777,12 +769,12 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -792,12 +784,12 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
@@ -807,7 +799,7 @@
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -837,7 +829,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -847,12 +839,12 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -862,12 +854,12 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
@@ -877,7 +869,7 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -907,7 +899,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -917,12 +909,12 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -932,12 +924,12 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
@@ -947,7 +939,7 @@
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -977,7 +969,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -987,12 +979,12 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -1002,12 +994,12 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
@@ -1017,7 +1009,7 @@
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -10521,7 +10513,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -10541,7 +10533,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -10601,33 +10593,33 @@
       <c r="B5" s="20" t="inlineStr">
         <is>
           <t>A | 514呎 (2房)
+招标单位
 -
+(在售)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 577呎 (3房)
+招标单位
 -
-(待售)</t>
-        </is>
-      </c>
-      <c r="C5" s="20" t="inlineStr">
-        <is>
-          <t>B | 577呎 (3房)
+(在售)</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>C | 737呎 (3房)
+招标单位
 -
+(在售)</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>D | 497呎 (2房)
+招标单位
 -
-(待售)</t>
-        </is>
-      </c>
-      <c r="D5" s="20" t="inlineStr">
-        <is>
-          <t>C | 737呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E5" s="20" t="inlineStr">
-        <is>
-          <t>D | 497呎 (2房)
--
--
-(待售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F5" s="21" t="inlineStr"/>
@@ -10665,7 +10657,7 @@
 (25年-01月-27日)</t>
         </is>
       </c>
-      <c r="E6" s="23" t="inlineStr">
+      <c r="E6" s="20" t="inlineStr">
         <is>
           <t>D | 340呎 (1房)
 $867万
@@ -10673,7 +10665,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F6" s="23" t="inlineStr">
+      <c r="F6" s="20" t="inlineStr">
         <is>
           <t>E | 324呎 (1房)
 $823万
@@ -10697,7 +10689,7 @@
 (26年-01月-22日)</t>
         </is>
       </c>
-      <c r="I6" s="23" t="inlineStr">
+      <c r="I6" s="20" t="inlineStr">
         <is>
           <t>H | 283呎 (1房)
 $725万
@@ -10744,7 +10736,7 @@
 (26年-08月-14日)</t>
         </is>
       </c>
-      <c r="F7" s="23" t="inlineStr">
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>E | 324呎 (1房)
 $812万
@@ -10768,7 +10760,7 @@
 (26年-01月-16日)</t>
         </is>
       </c>
-      <c r="I7" s="23" t="inlineStr">
+      <c r="I7" s="20" t="inlineStr">
         <is>
           <t>H | 283呎 (1房)
 $715万
@@ -10839,7 +10831,7 @@
 (25年-11月-21日)</t>
         </is>
       </c>
-      <c r="I8" s="23" t="inlineStr">
+      <c r="I8" s="20" t="inlineStr">
         <is>
           <t>H | 283呎 (1房)
 $697万
